--- a/salidas/empresas/AVGO.xlsx
+++ b/salidas/empresas/AVGO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B2" t="n">
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B3" t="n">
-        <v>1.195878267288208</v>
+        <v>1.195878386497498</v>
       </c>
       <c r="C3" t="n">
         <v>1.707000017166138</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B4" t="n">
-        <v>1.050859928131104</v>
+        <v>1.050859570503235</v>
       </c>
       <c r="C4" t="n">
         <v>1.5</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B5" t="n">
-        <v>1.111108899116516</v>
+        <v>1.111108541488647</v>
       </c>
       <c r="C5" t="n">
         <v>1.585999965667725</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B6" t="n">
-        <v>1.281347990036011</v>
+        <v>1.28134822845459</v>
       </c>
       <c r="C6" t="n">
         <v>1.828999996185303</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B7" t="n">
-        <v>1.217595815658569</v>
+        <v>1.217595458030701</v>
       </c>
       <c r="C7" t="n">
         <v>1.73800003528595</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B8" t="n">
-        <v>1.271540403366089</v>
+        <v>1.271539926528931</v>
       </c>
       <c r="C8" t="n">
         <v>1.815000057220459</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B9" t="n">
-        <v>1.440378069877625</v>
+        <v>1.440377712249756</v>
       </c>
       <c r="C9" t="n">
         <v>2.055999994277954</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B10" t="n">
-        <v>1.436875224113464</v>
+        <v>1.436875343322754</v>
       </c>
       <c r="C10" t="n">
         <v>2.051000118255615</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B11" t="n">
-        <v>1.446683526039124</v>
+        <v>1.446683645248413</v>
       </c>
       <c r="C11" t="n">
         <v>2.065000057220459</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B12" t="n">
-        <v>1.475406885147095</v>
+        <v>1.475406527519226</v>
       </c>
       <c r="C12" t="n">
         <v>2.105999946594238</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B13" t="n">
-        <v>1.524446606636047</v>
+        <v>1.524446725845337</v>
       </c>
       <c r="C13" t="n">
         <v>2.176000118255615</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B14" t="n">
-        <v>1.411654829978943</v>
+        <v>1.411654472351074</v>
       </c>
       <c r="C14" t="n">
         <v>2.015000104904175</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B15" t="n">
-        <v>1.576990246772766</v>
+        <v>1.576989531517029</v>
       </c>
       <c r="C15" t="n">
         <v>2.250999927520752</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B16" t="n">
-        <v>1.729014039039612</v>
+        <v>1.72901451587677</v>
       </c>
       <c r="C16" t="n">
         <v>2.467999935150146</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B17" t="n">
-        <v>1.829196453094482</v>
+        <v>1.829195737838745</v>
       </c>
       <c r="C17" t="n">
         <v>2.611000061035156</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B18" t="n">
-        <v>1.995620250701904</v>
+        <v>1.995619297027588</v>
       </c>
       <c r="C18" t="n">
         <v>2.841000080108643</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B19" t="n">
-        <v>2.0166916847229</v>
+        <v>2.016693115234375</v>
       </c>
       <c r="C19" t="n">
         <v>2.871000051498413</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B20" t="n">
-        <v>2.387578248977661</v>
+        <v>2.38757848739624</v>
       </c>
       <c r="C20" t="n">
         <v>3.398999929428101</v>
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B21" t="n">
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B22" t="n">
-        <v>2.356416940689087</v>
+        <v>2.356416463851929</v>
       </c>
       <c r="C22" t="n">
         <v>3.345999956130981</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B23" t="n">
-        <v>2.379656076431274</v>
+        <v>2.379656553268433</v>
       </c>
       <c r="C23" t="n">
         <v>3.378999948501587</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B24" t="n">
-        <v>2.683202743530273</v>
+        <v>2.683202981948853</v>
       </c>
       <c r="C24" t="n">
         <v>3.799999952316284</v>
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B25" t="n">
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B26" t="n">
-        <v>2.337916851043701</v>
+        <v>2.337917327880859</v>
       </c>
       <c r="C26" t="n">
         <v>3.311000108718872</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B27" t="n">
-        <v>2.320891380310059</v>
+        <v>2.320893287658691</v>
       </c>
       <c r="C27" t="n">
         <v>3.276999950408936</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B28" t="n">
-        <v>2.391716480255127</v>
+        <v>2.391716241836548</v>
       </c>
       <c r="C28" t="n">
         <v>3.377000093460083</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B29" t="n">
-        <v>2.119044780731201</v>
+        <v>2.11904501914978</v>
       </c>
       <c r="C29" t="n">
         <v>2.992000102996826</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B30" t="n">
-        <v>2.052550792694092</v>
+        <v>2.052550315856934</v>
       </c>
       <c r="C30" t="n">
         <v>2.885999917984009</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B31" t="n">
-        <v>2.413845539093018</v>
+        <v>2.413844585418701</v>
       </c>
       <c r="C31" t="n">
         <v>3.394000053405762</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B32" t="n">
-        <v>2.674858331680298</v>
+        <v>2.674859046936035</v>
       </c>
       <c r="C32" t="n">
         <v>3.760999917984009</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B33" t="n">
-        <v>2.78132700920105</v>
+        <v>2.781326293945312</v>
       </c>
       <c r="C33" t="n">
         <v>3.897000074386597</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B34" t="n">
-        <v>2.460870742797852</v>
+        <v>2.460870504379272</v>
       </c>
       <c r="C34" t="n">
         <v>3.447999954223633</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B35" t="n">
-        <v>2.362379789352417</v>
+        <v>2.362379312515259</v>
       </c>
       <c r="C35" t="n">
         <v>3.309999942779541</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B36" t="n">
-        <v>2.573558568954468</v>
+        <v>2.573559045791626</v>
       </c>
       <c r="C36" t="n">
         <v>3.589999914169312</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B37" t="n">
-        <v>2.64524507522583</v>
+        <v>2.645244836807251</v>
       </c>
       <c r="C37" t="n">
         <v>3.690000057220459</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B38" t="n">
-        <v>2.621588706970215</v>
+        <v>2.621588945388794</v>
       </c>
       <c r="C38" t="n">
         <v>3.657000064849854</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B39" t="n">
-        <v>2.511108875274658</v>
+        <v>2.511109113693237</v>
       </c>
       <c r="C39" t="n">
         <v>3.486999988555908</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B42" t="n">
-        <v>2.290488958358765</v>
+        <v>2.290488481521606</v>
       </c>
       <c r="C42" t="n">
         <v>3.164999961853027</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B43" t="n">
-        <v>2.588650941848755</v>
+        <v>2.588651895523071</v>
       </c>
       <c r="C43" t="n">
         <v>3.57699990272522</v>
@@ -1280,11 +1292,11 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B44" t="n">
-        <v>2.476478576660156</v>
+        <v>2.476477861404419</v>
       </c>
       <c r="C44" t="n">
         <v>3.421999931335449</v>
@@ -1299,11 +1311,11 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B45" t="n">
-        <v>2.613325595855713</v>
+        <v>2.613326787948608</v>
       </c>
       <c r="C45" t="n">
         <v>3.592000007629395</v>
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B47" t="n">
-        <v>2.745011568069458</v>
+        <v>2.7450110912323</v>
       </c>
       <c r="C47" t="n">
         <v>3.773000001907349</v>
@@ -1356,11 +1368,11 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B48" t="n">
-        <v>2.735512971878052</v>
+        <v>2.735512733459473</v>
       </c>
       <c r="C48" t="n">
         <v>3.73799991607666</v>
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B49" t="n">
-        <v>2.684285879135132</v>
+        <v>2.684285163879395</v>
       </c>
       <c r="C49" t="n">
         <v>3.667999982833862</v>
@@ -1394,11 +1406,11 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B50" t="n">
-        <v>2.818207263946533</v>
+        <v>2.818207740783691</v>
       </c>
       <c r="C50" t="n">
         <v>3.851000070571899</v>
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B51" t="n">
-        <v>3.171215295791626</v>
+        <v>3.171214580535889</v>
       </c>
       <c r="C51" t="n">
         <v>4.308000087738037</v>
@@ -1432,11 +1444,11 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B52" t="n">
-        <v>3.344203233718872</v>
+        <v>3.34420371055603</v>
       </c>
       <c r="C52" t="n">
         <v>4.543000221252441</v>
@@ -1451,11 +1463,11 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B53" t="n">
-        <v>3.292675018310547</v>
+        <v>3.292674541473389</v>
       </c>
       <c r="C53" t="n">
         <v>4.473000049591064</v>
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B54" t="n">
-        <v>3.910867691040039</v>
+        <v>3.910867929458618</v>
       </c>
       <c r="C54" t="n">
         <v>5.288000106811523</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B55" t="n">
-        <v>4.041034698486328</v>
+        <v>4.041033744812012</v>
       </c>
       <c r="C55" t="n">
         <v>5.464000225067139</v>
@@ -1508,7 +1520,7 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B56" t="n">
@@ -1527,11 +1539,11 @@
       <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B57" t="n">
-        <v>4.783968448638916</v>
+        <v>4.783967018127441</v>
       </c>
       <c r="C57" t="n">
         <v>6.440999984741211</v>
@@ -1546,11 +1558,11 @@
       <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B58" t="n">
-        <v>4.716379642486572</v>
+        <v>4.716378211975098</v>
       </c>
       <c r="C58" t="n">
         <v>6.349999904632568</v>
@@ -1565,11 +1577,11 @@
       <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B59" t="n">
-        <v>5.248920917510986</v>
+        <v>5.248920440673828</v>
       </c>
       <c r="C59" t="n">
         <v>7.066999912261963</v>
@@ -1584,11 +1596,11 @@
       <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B60" t="n">
-        <v>5.374895095825195</v>
+        <v>5.374894618988037</v>
       </c>
       <c r="C60" t="n">
         <v>7.206999778747559</v>
@@ -1603,11 +1615,11 @@
       <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B61" t="n">
-        <v>5.174277305603027</v>
+        <v>5.174278259277344</v>
       </c>
       <c r="C61" t="n">
         <v>6.938000202178955</v>
@@ -1622,11 +1634,11 @@
       <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B62" t="n">
-        <v>6.122173309326172</v>
+        <v>6.122174739837646</v>
       </c>
       <c r="C62" t="n">
         <v>8.208999633789062</v>
@@ -1641,11 +1653,11 @@
       <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B63" t="n">
-        <v>6.512058258056641</v>
+        <v>6.512057781219482</v>
       </c>
       <c r="C63" t="n">
         <v>8.699999809265137</v>
@@ -1660,11 +1672,11 @@
       <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B64" t="n">
-        <v>6.455921649932861</v>
+        <v>6.455920696258545</v>
       </c>
       <c r="C64" t="n">
         <v>8.625</v>
@@ -1679,11 +1691,11 @@
       <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B65" t="n">
-        <v>6.991108417510986</v>
+        <v>6.991107940673828</v>
       </c>
       <c r="C65" t="n">
         <v>9.340000152587891</v>
@@ -1698,11 +1710,11 @@
       <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B66" t="n">
-        <v>7.556458473205566</v>
+        <v>7.556460380554199</v>
       </c>
       <c r="C66" t="n">
         <v>10.05900001525879</v>
@@ -1717,7 +1729,7 @@
       <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B67" t="n">
@@ -1736,11 +1748,11 @@
       <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B68" t="n">
-        <v>9.586989402770996</v>
+        <v>9.586994171142578</v>
       </c>
       <c r="C68" t="n">
         <v>12.76200008392334</v>
@@ -1755,11 +1767,11 @@
       <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B69" t="n">
-        <v>9.567074775695801</v>
+        <v>9.567072868347168</v>
       </c>
       <c r="C69" t="n">
         <v>12.69799995422363</v>
@@ -1774,7 +1786,7 @@
       <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B70" t="n">
@@ -1793,11 +1805,11 @@
       <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B71" t="n">
-        <v>11.15606498718262</v>
+        <v>11.1560640335083</v>
       </c>
       <c r="C71" t="n">
         <v>14.80700016021729</v>
@@ -1812,11 +1824,11 @@
       <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B72" t="n">
-        <v>10.04365730285645</v>
+        <v>10.04366207122803</v>
       </c>
       <c r="C72" t="n">
         <v>13.29300022125244</v>
@@ -1831,11 +1843,11 @@
       <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B73" t="n">
-        <v>9.455079078674316</v>
+        <v>9.455080986022949</v>
       </c>
       <c r="C73" t="n">
         <v>12.51399993896484</v>
@@ -1850,11 +1862,11 @@
       <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B74" t="n">
-        <v>9.517786026000977</v>
+        <v>9.517789840698242</v>
       </c>
       <c r="C74" t="n">
         <v>12.59700012207031</v>
@@ -1869,11 +1881,11 @@
       <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B75" t="n">
-        <v>9.474871635437012</v>
+        <v>9.474870681762695</v>
       </c>
       <c r="C75" t="n">
         <v>12.50100040435791</v>
@@ -1888,11 +1900,11 @@
       <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B76" t="n">
-        <v>9.332378387451172</v>
+        <v>9.332379341125488</v>
       </c>
       <c r="C76" t="n">
         <v>12.3129997253418</v>
@@ -1907,7 +1919,7 @@
       <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B77" t="n">
@@ -1926,7 +1938,7 @@
       <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B78" t="n">
@@ -1945,11 +1957,11 @@
       <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B79" t="n">
-        <v>10.16548824310303</v>
+        <v>10.16548538208008</v>
       </c>
       <c r="C79" t="n">
         <v>13.37100028991699</v>
@@ -1964,11 +1976,11 @@
       <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B80" t="n">
-        <v>10.18525695800781</v>
+        <v>10.18525409698486</v>
       </c>
       <c r="C80" t="n">
         <v>13.39700031280518</v>
@@ -1983,11 +1995,11 @@
       <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B81" t="n">
-        <v>11.78497123718262</v>
+        <v>11.7849702835083</v>
       </c>
       <c r="C81" t="n">
         <v>15.44999980926514</v>
@@ -2002,11 +2014,11 @@
       <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B82" t="n">
-        <v>11.11753559112549</v>
+        <v>11.11753749847412</v>
       </c>
       <c r="C82" t="n">
         <v>14.57499980926514</v>
@@ -2021,11 +2033,11 @@
       <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B83" t="n">
-        <v>11.77429103851318</v>
+        <v>11.77429294586182</v>
       </c>
       <c r="C83" t="n">
         <v>15.43599987030029</v>
@@ -2040,11 +2052,11 @@
       <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B84" t="n">
-        <v>11.89101600646973</v>
+        <v>11.89101505279541</v>
       </c>
       <c r="C84" t="n">
         <v>15.53999996185303</v>
@@ -2059,7 +2071,7 @@
       <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B85" t="n">
@@ -2078,11 +2090,11 @@
       <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B86" t="n">
-        <v>13.49943828582764</v>
+        <v>13.49944019317627</v>
       </c>
       <c r="C86" t="n">
         <v>17.64200019836426</v>
@@ -2097,11 +2109,11 @@
       <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B87" t="n">
-        <v>13.24083423614502</v>
+        <v>13.24083137512207</v>
       </c>
       <c r="C87" t="n">
         <v>17.25200080871582</v>
@@ -2116,7 +2128,7 @@
       <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B88" t="n">
@@ -2135,11 +2147,11 @@
       <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B89" t="n">
-        <v>13.08502864837646</v>
+        <v>13.08502578735352</v>
       </c>
       <c r="C89" t="n">
         <v>17.04899978637695</v>
@@ -2154,11 +2166,11 @@
       <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B90" t="n">
-        <v>13.64457988739014</v>
+        <v>13.64457893371582</v>
       </c>
       <c r="C90" t="n">
         <v>17.67700004577637</v>
@@ -2173,11 +2185,11 @@
       <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B91" t="n">
-        <v>15.39906311035156</v>
+        <v>15.39907073974609</v>
       </c>
       <c r="C91" t="n">
         <v>19.95000076293945</v>
@@ -2192,11 +2204,11 @@
       <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B92" t="n">
-        <v>16.28132438659668</v>
+        <v>16.28132820129395</v>
       </c>
       <c r="C92" t="n">
         <v>21.0930004119873</v>
@@ -2211,11 +2223,11 @@
       <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B93" t="n">
-        <v>16.97780227661133</v>
+        <v>16.97779655456543</v>
       </c>
       <c r="C93" t="n">
         <v>21.89599990844727</v>
@@ -2230,11 +2242,11 @@
       <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B94" t="n">
-        <v>17.12124252319336</v>
+        <v>17.12124443054199</v>
       </c>
       <c r="C94" t="n">
         <v>22.08099937438965</v>
@@ -2249,7 +2261,7 @@
       <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B95" t="n">
@@ -2268,11 +2280,11 @@
       <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B96" t="n">
-        <v>18.14727020263672</v>
+        <v>18.14726638793945</v>
       </c>
       <c r="C96" t="n">
         <v>23.30500030517578</v>
@@ -2287,11 +2299,11 @@
       <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B97" t="n">
-        <v>19.20705986022949</v>
+        <v>19.20705795288086</v>
       </c>
       <c r="C97" t="n">
         <v>24.66600036621094</v>
@@ -2306,11 +2318,11 @@
       <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B98" t="n">
-        <v>19.62832641601562</v>
+        <v>19.62833213806152</v>
       </c>
       <c r="C98" t="n">
         <v>25.20700073242188</v>
@@ -2325,11 +2337,11 @@
       <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B99" t="n">
-        <v>18.96344947814941</v>
+        <v>18.96344375610352</v>
       </c>
       <c r="C99" t="n">
         <v>24.25399971008301</v>
@@ -2344,11 +2356,11 @@
       <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B100" t="n">
-        <v>20.63430213928223</v>
+        <v>20.63430023193359</v>
       </c>
       <c r="C100" t="n">
         <v>26.39100074768066</v>
@@ -2363,11 +2375,11 @@
       <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B101" t="n">
-        <v>21.73125648498535</v>
+        <v>21.73126220703125</v>
       </c>
       <c r="C101" t="n">
         <v>27.79400062561035</v>
@@ -2382,11 +2394,11 @@
       <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B102" t="n">
-        <v>20.21936798095703</v>
+        <v>20.2193660736084</v>
       </c>
       <c r="C102" t="n">
         <v>25.69000053405762</v>
@@ -2401,11 +2413,11 @@
       <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B103" t="n">
-        <v>19.52124786376953</v>
+        <v>19.52124977111816</v>
       </c>
       <c r="C103" t="n">
         <v>24.80299949645996</v>
@@ -2420,11 +2432,11 @@
       <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B104" t="n">
-        <v>19.39768218994141</v>
+        <v>19.39767646789551</v>
       </c>
       <c r="C104" t="n">
         <v>24.64599990844727</v>
@@ -2439,11 +2451,11 @@
       <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B105" t="n">
-        <v>18.81864547729492</v>
+        <v>18.81864166259766</v>
       </c>
       <c r="C105" t="n">
         <v>23.56500053405762</v>
@@ -2458,11 +2470,11 @@
       <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B106" t="n">
-        <v>18.32112312316895</v>
+        <v>18.32112693786621</v>
       </c>
       <c r="C106" t="n">
         <v>22.9419994354248</v>
@@ -2477,11 +2489,11 @@
       <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B107" t="n">
-        <v>20.12991905212402</v>
+        <v>20.12992858886719</v>
       </c>
       <c r="C107" t="n">
         <v>25.20700073242188</v>
@@ -2496,11 +2508,11 @@
       <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B108" t="n">
-        <v>19.63669395446777</v>
+        <v>19.63669776916504</v>
       </c>
       <c r="C108" t="n">
         <v>24.26399993896484</v>
@@ -2521,11 +2533,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B109" t="n">
-        <v>17.94770622253418</v>
+        <v>17.94770050048828</v>
       </c>
       <c r="C109" t="n">
         <v>22.17700004577637</v>
@@ -2546,11 +2558,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B110" t="n">
-        <v>17.72595405578613</v>
+        <v>17.7259578704834</v>
       </c>
       <c r="C110" t="n">
         <v>21.90299987792969</v>
@@ -2571,11 +2583,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B111" t="n">
-        <v>20.11761856079102</v>
+        <v>20.11762237548828</v>
       </c>
       <c r="C111" t="n">
         <v>24.67300033569336</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B112" t="n">
-        <v>18.22270011901855</v>
+        <v>18.22270584106445</v>
       </c>
       <c r="C112" t="n">
         <v>22.34900093078613</v>
@@ -2621,7 +2633,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B113" t="n">
@@ -2646,11 +2658,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B114" t="n">
-        <v>20.95170211791992</v>
+        <v>20.95170402526855</v>
       </c>
       <c r="C114" t="n">
         <v>25.42799949645996</v>
@@ -2675,11 +2687,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B115" t="n">
-        <v>22.10278129577637</v>
+        <v>22.10277366638184</v>
       </c>
       <c r="C115" t="n">
         <v>26.82500076293945</v>
@@ -2704,11 +2716,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B116" t="n">
-        <v>22.68861770629883</v>
+        <v>22.68861198425293</v>
       </c>
       <c r="C116" t="n">
         <v>27.5359992980957</v>
@@ -2733,11 +2745,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B117" t="n">
-        <v>24.99868965148926</v>
+        <v>24.99869155883789</v>
       </c>
       <c r="C117" t="n">
         <v>30.07099914550781</v>
@@ -2762,11 +2774,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B118" t="n">
-        <v>26.46929740905762</v>
+        <v>26.46929550170898</v>
       </c>
       <c r="C118" t="n">
         <v>31.84000015258789</v>
@@ -2791,11 +2803,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B119" t="n">
-        <v>20.91938972473145</v>
+        <v>20.91939163208008</v>
       </c>
       <c r="C119" t="n">
         <v>25.16399955749512</v>
@@ -2820,11 +2832,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B120" t="n">
-        <v>24.15987014770508</v>
+        <v>24.15987586975098</v>
       </c>
       <c r="C120" t="n">
         <v>28.7859992980957</v>
@@ -2849,11 +2861,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B121" t="n">
-        <v>24.33864402770996</v>
+        <v>24.33864212036133</v>
       </c>
       <c r="C121" t="n">
         <v>28.99900054931641</v>
@@ -2878,11 +2890,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B122" t="n">
-        <v>23.72176361083984</v>
+        <v>23.72176742553711</v>
       </c>
       <c r="C122" t="n">
         <v>28.26399993896484</v>
@@ -2907,11 +2919,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B123" t="n">
-        <v>23.38355255126953</v>
+        <v>23.38355445861816</v>
       </c>
       <c r="C123" t="n">
         <v>27.60700035095215</v>
@@ -2936,11 +2948,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B124" t="n">
-        <v>24.80484771728516</v>
+        <v>24.80484580993652</v>
       </c>
       <c r="C124" t="n">
         <v>29.28499984741211</v>
@@ -2965,7 +2977,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B125" t="n">
@@ -2994,11 +3006,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B126" t="n">
-        <v>27.03851509094238</v>
+        <v>27.03851699829102</v>
       </c>
       <c r="C126" t="n">
         <v>31.60199928283691</v>
@@ -3023,11 +3035,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B127" t="n">
-        <v>26.10934257507324</v>
+        <v>26.10934066772461</v>
       </c>
       <c r="C127" t="n">
         <v>30.51600074768066</v>
@@ -3052,11 +3064,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B128" t="n">
-        <v>23.32523536682129</v>
+        <v>23.32522964477539</v>
       </c>
       <c r="C128" t="n">
         <v>27.26199913024902</v>
@@ -3081,11 +3093,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B129" t="n">
-        <v>20.6309814453125</v>
+        <v>20.6309757232666</v>
       </c>
       <c r="C129" t="n">
         <v>23.70999908447266</v>
@@ -3110,7 +3122,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B130" t="n">
@@ -3139,11 +3151,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B131" t="n">
-        <v>25.34452438354492</v>
+        <v>25.34452247619629</v>
       </c>
       <c r="C131" t="n">
         <v>29.12700080871582</v>
@@ -3168,11 +3180,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B132" t="n">
-        <v>27.74537086486816</v>
+        <v>27.74536895751953</v>
       </c>
       <c r="C132" t="n">
         <v>31.56100082397461</v>
@@ -3197,11 +3209,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B133" t="n">
-        <v>27.8455867767334</v>
+        <v>27.84558486938477</v>
       </c>
       <c r="C133" t="n">
         <v>31.67499923706055</v>
@@ -3226,11 +3238,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B134" t="n">
-        <v>30.51805686950684</v>
+        <v>30.51805877685547</v>
       </c>
       <c r="C134" t="n">
         <v>34.71500015258789</v>
@@ -3255,11 +3267,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B135" t="n">
-        <v>32.31947326660156</v>
+        <v>32.31946182250977</v>
       </c>
       <c r="C135" t="n">
         <v>36.43199920654297</v>
@@ -3284,11 +3296,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B136" t="n">
-        <v>31.01628875732422</v>
+        <v>31.01629638671875</v>
       </c>
       <c r="C136" t="n">
         <v>34.9630012512207</v>
@@ -3313,11 +3325,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B137" t="n">
-        <v>35.62486267089844</v>
+        <v>35.62487030029297</v>
       </c>
       <c r="C137" t="n">
         <v>40.15800094604492</v>
@@ -3342,7 +3354,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B138" t="n">
@@ -3371,7 +3383,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B139" t="n">
@@ -3400,7 +3412,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B140" t="n">
@@ -3429,11 +3441,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B141" t="n">
-        <v>41.80682373046875</v>
+        <v>41.80683517456055</v>
       </c>
       <c r="C141" t="n">
         <v>46.36600112915039</v>
@@ -3458,7 +3470,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B142" t="n">
@@ -3487,11 +3499,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B143" t="n">
-        <v>42.58858108520508</v>
+        <v>42.58857727050781</v>
       </c>
       <c r="C143" t="n">
         <v>47.23300170898438</v>
@@ -3516,11 +3528,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B144" t="n">
-        <v>43.33177947998047</v>
+        <v>43.33178329467773</v>
       </c>
       <c r="C144" t="n">
         <v>47.68399810791016</v>
@@ -3545,11 +3557,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B145" t="n">
-        <v>44.10965728759766</v>
+        <v>44.10965347290039</v>
       </c>
       <c r="C145" t="n">
         <v>48.54000091552734</v>
@@ -3574,11 +3586,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B146" t="n">
-        <v>45.182861328125</v>
+        <v>45.18286895751953</v>
       </c>
       <c r="C146" t="n">
         <v>49.72100067138672</v>
@@ -3603,11 +3615,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B147" t="n">
-        <v>44.38990020751953</v>
+        <v>44.38990783691406</v>
       </c>
       <c r="C147" t="n">
         <v>48.49300003051758</v>
@@ -3632,11 +3644,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B148" t="n">
-        <v>48.66841888427734</v>
+        <v>48.66842651367188</v>
       </c>
       <c r="C148" t="n">
         <v>53.16699981689453</v>
@@ -3661,7 +3673,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B149" t="n">
@@ -3690,7 +3702,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B150" t="n">
@@ -3719,11 +3731,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B151" t="n">
-        <v>53.97381973266602</v>
+        <v>53.97380828857422</v>
       </c>
       <c r="C151" t="n">
         <v>58.5880012512207</v>
@@ -3748,11 +3760,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B152" t="n">
-        <v>54.11753082275391</v>
+        <v>54.11753845214844</v>
       </c>
       <c r="C152" t="n">
         <v>58.74399948120117</v>
@@ -3777,7 +3789,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B153" t="n">
@@ -3806,11 +3818,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B154" t="n">
-        <v>51.41818618774414</v>
+        <v>51.41819381713867</v>
       </c>
       <c r="C154" t="n">
         <v>55.43899917602539</v>
@@ -3835,11 +3847,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B155" t="n">
-        <v>53.80550003051758</v>
+        <v>53.80549621582031</v>
       </c>
       <c r="C155" t="n">
         <v>58.01300048828125</v>
@@ -3864,11 +3876,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B156" t="n">
-        <v>45.43111419677734</v>
+        <v>45.43111801147461</v>
       </c>
       <c r="C156" t="n">
         <v>48.58100128173828</v>
@@ -3893,7 +3905,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B157" t="n">
@@ -3922,11 +3934,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B158" t="n">
-        <v>46.67488861083984</v>
+        <v>46.67488479614258</v>
       </c>
       <c r="C158" t="n">
         <v>49.9109992980957</v>
@@ -3951,7 +3963,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B159" t="n">
@@ -3980,11 +3992,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B160" t="n">
-        <v>44.33249664306641</v>
+        <v>44.33249282836914</v>
       </c>
       <c r="C160" t="n">
         <v>47.01200103759766</v>
@@ -4009,11 +4021,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B161" t="n">
-        <v>51.96233367919922</v>
+        <v>51.96234130859375</v>
       </c>
       <c r="C161" t="n">
         <v>55.10300064086914</v>
@@ -4038,11 +4050,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B162" t="n">
-        <v>53.16611099243164</v>
+        <v>53.16609954833984</v>
       </c>
       <c r="C162" t="n">
         <v>55.91299819946289</v>
@@ -4067,11 +4079,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B163" t="n">
-        <v>55.62696075439453</v>
+        <v>55.6269645690918</v>
       </c>
       <c r="C163" t="n">
         <v>58.50099945068359</v>
@@ -4096,11 +4108,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B164" t="n">
-        <v>56.50937271118164</v>
+        <v>56.50938034057617</v>
       </c>
       <c r="C164" t="n">
         <v>59.42900085449219</v>
@@ -4125,11 +4137,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B165" t="n">
-        <v>61.44130706787109</v>
+        <v>61.44131088256836</v>
       </c>
       <c r="C165" t="n">
         <v>64.15399932861328</v>
@@ -4154,11 +4166,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B166" t="n">
-        <v>60.00090026855469</v>
+        <v>60.00090408325195</v>
       </c>
       <c r="C166" t="n">
         <v>62.65000152587891</v>
@@ -4183,11 +4195,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B167" t="n">
-        <v>77.37960052490234</v>
+        <v>77.37961578369141</v>
       </c>
       <c r="C167" t="n">
         <v>80.79599761962891</v>
@@ -4212,11 +4224,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B168" t="n">
-        <v>83.51772308349609</v>
+        <v>83.51773834228516</v>
       </c>
       <c r="C168" t="n">
         <v>86.74299621582031</v>
@@ -4241,11 +4253,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B169" t="n">
-        <v>86.52365875244141</v>
+        <v>86.52365112304688</v>
       </c>
       <c r="C169" t="n">
         <v>89.86499786376953</v>
@@ -4270,11 +4282,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B170" t="n">
-        <v>88.85752105712891</v>
+        <v>88.85752868652344</v>
       </c>
       <c r="C170" t="n">
         <v>92.28900146484375</v>
@@ -4299,7 +4311,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B171" t="n">
@@ -4328,11 +4340,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B172" t="n">
-        <v>81.44984436035156</v>
+        <v>81.44983673095703</v>
       </c>
       <c r="C172" t="n">
         <v>84.13700103759766</v>
@@ -4357,11 +4369,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B173" t="n">
-        <v>89.61640930175781</v>
+        <v>89.61641693115234</v>
       </c>
       <c r="C173" t="n">
         <v>92.572998046875</v>
@@ -4386,7 +4398,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B174" t="n">
@@ -4415,11 +4427,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B175" t="n">
-        <v>114.7565841674805</v>
+        <v>114.756591796875</v>
       </c>
       <c r="C175" t="n">
         <v>118</v>
@@ -4444,11 +4456,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B176" t="n">
-        <v>126.4744262695312</v>
+        <v>126.4743957519531</v>
       </c>
       <c r="C176" t="n">
         <v>130.0489959716797</v>
@@ -4473,11 +4485,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B177" t="n">
-        <v>129.4468536376953</v>
+        <v>129.4468383789062</v>
       </c>
       <c r="C177" t="n">
         <v>132.5410003662109</v>
@@ -4502,11 +4514,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B178" t="n">
-        <v>126.9915237426758</v>
+        <v>126.9915390014648</v>
       </c>
       <c r="C178" t="n">
         <v>130.0269927978516</v>
@@ -4531,11 +4543,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B179" t="n">
-        <v>129.7534942626953</v>
+        <v>129.7535095214844</v>
       </c>
       <c r="C179" t="n">
         <v>132.8549957275391</v>
@@ -4560,7 +4572,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B180" t="n">
@@ -4589,11 +4601,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B181" t="n">
-        <v>157.4272308349609</v>
+        <v>157.42724609375</v>
       </c>
       <c r="C181" t="n">
         <v>160.6799926757812</v>
@@ -4618,11 +4630,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B182" t="n">
-        <v>159.5239410400391</v>
+        <v>159.52392578125</v>
       </c>
       <c r="C182" t="n">
         <v>162.8200073242188</v>
@@ -4647,7 +4659,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B183" t="n">
@@ -4676,11 +4688,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B184" t="n">
-        <v>166.8802947998047</v>
+        <v>166.8803253173828</v>
       </c>
       <c r="C184" t="n">
         <v>169.7700042724609</v>
@@ -4705,7 +4717,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B185" t="n">
@@ -4734,7 +4746,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B186" t="n">
@@ -4763,11 +4775,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B187" t="n">
-        <v>218.0864715576172</v>
+        <v>218.0865020751953</v>
       </c>
       <c r="C187" t="n">
         <v>221.2700042724609</v>
@@ -4792,7 +4804,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B188" t="n">
@@ -4821,7 +4833,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B189" t="n">
@@ -4850,7 +4862,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B190" t="n">
@@ -4879,7 +4891,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B191" t="n">
@@ -4908,11 +4920,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B192" t="n">
-        <v>273.1475524902344</v>
+        <v>273.1475830078125</v>
       </c>
       <c r="C192" t="n">
         <v>275.6499938964844</v>
@@ -4937,11 +4949,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B193" t="n">
-        <v>291.0337219238281</v>
+        <v>291.0337829589844</v>
       </c>
       <c r="C193" t="n">
         <v>293.7000122070312</v>
@@ -4966,7 +4978,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B194" t="n">
@@ -4995,11 +5007,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B195" t="n">
-        <v>327.4751281738281</v>
+        <v>327.4751586914062</v>
       </c>
       <c r="C195" t="n">
         <v>329.9100036621094</v>
@@ -5024,11 +5036,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B196" t="n">
-        <v>366.9019470214844</v>
+        <v>366.9020080566406</v>
       </c>
       <c r="C196" t="n">
         <v>369.6300048828125</v>
@@ -5053,7 +5065,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B197" t="n">
@@ -5082,11 +5094,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B198" t="n">
-        <v>344.2030029296875</v>
+        <v>344.2029724121094</v>
       </c>
       <c r="C198" t="n">
         <v>346.1000061035156</v>
@@ -5111,11 +5123,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B199" t="n">
-        <v>329.4840698242188</v>
+        <v>329.4841003417969</v>
       </c>
       <c r="C199" t="n">
         <v>331.2999877929688</v>
@@ -5140,7 +5152,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B200" t="n">
@@ -5169,11 +5181,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B201" t="n">
-        <v>308.4592590332031</v>
+        <v>308.459228515625</v>
       </c>
       <c r="C201" t="n">
         <v>309.510009765625</v>
@@ -5198,7 +5210,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B202" t="n">
@@ -5227,7 +5239,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B203" t="n">
@@ -5256,7 +5268,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B204" t="n">
@@ -5285,7 +5297,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B205" t="n">
@@ -5314,7 +5326,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B206" t="n">
@@ -5343,32 +5355,32 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B207" t="n">
-        <v>354.989990234375</v>
+        <v>350.3599853515625</v>
       </c>
       <c r="C207" t="n">
-        <v>354.989990234375</v>
+        <v>350.3599853515625</v>
       </c>
       <c r="D207" t="n">
-        <v>472238300</v>
+        <v>493179500</v>
       </c>
       <c r="E207" t="n">
         <v>7.84</v>
       </c>
       <c r="F207" t="n">
-        <v>45.27933548907844</v>
+        <v>44.68877364178093</v>
       </c>
       <c r="G207" t="n">
         <v>4773629865</v>
       </c>
       <c r="H207" t="n">
-        <v>1694590819158.871</v>
+        <v>1672488889575.181</v>
       </c>
       <c r="I207" t="n">
-        <v>0.09892645918411606</v>
+        <v>0.103313309566786</v>
       </c>
     </row>
   </sheetData>
@@ -5400,75 +5412,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>42674</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>42764</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -5504,13 +5516,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>42765</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>42855</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>43265</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -5546,13 +5558,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>42856</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>42946</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>43356</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -5588,13 +5600,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>42947</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43037</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -5621,7 +5633,7 @@
       <c r="I5" t="n">
         <v>0.401</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="K5" t="n">
@@ -5634,13 +5646,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43038</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43135</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -5667,7 +5679,7 @@
       <c r="I6" t="n">
         <v>1.806</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="K6" t="n">
@@ -5680,13 +5692,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43136</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43226</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>43265</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -5713,7 +5725,7 @@
       <c r="I7" t="n">
         <v>2.534</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="K7" t="n">
@@ -5726,13 +5738,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43227</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43317</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>43356</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -5759,7 +5771,7 @@
       <c r="I8" t="n">
         <v>2.691</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="K8" t="n">
@@ -5772,13 +5784,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43318</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43408</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -5805,7 +5817,7 @@
       <c r="I9" t="n">
         <v>2.83</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="K9" t="n">
@@ -5818,13 +5830,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43409</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43499</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -5851,7 +5863,7 @@
       <c r="I10" t="n">
         <v>1.48</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="K10" t="n">
@@ -5864,13 +5876,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>43500</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>43590</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -5897,7 +5909,7 @@
       <c r="I11" t="n">
         <v>0.8110000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="K11" t="n">
@@ -5910,13 +5922,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>43591</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>43681</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -5943,7 +5955,7 @@
       <c r="I12" t="n">
         <v>0.711</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="K12" t="n">
@@ -5956,13 +5968,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>43682</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>43772</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -5989,7 +6001,7 @@
       <c r="I13" t="n">
         <v>0.644</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="K13" t="n">
@@ -6002,13 +6014,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>43773</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>43863</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -6035,7 +6047,7 @@
       <c r="I14" t="n">
         <v>0.606</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="K14" t="n">
@@ -6048,13 +6060,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>43864</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>43954</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -6081,7 +6093,7 @@
       <c r="I15" t="n">
         <v>0.5589999999999999</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="K15" t="n">
@@ -6094,13 +6106,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>43955</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44045</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -6127,7 +6139,7 @@
       <c r="I16" t="n">
         <v>0.533</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="K16" t="n">
@@ -6140,13 +6152,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44046</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44136</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -6173,7 +6185,7 @@
       <c r="I17" t="n">
         <v>0.629</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="K17" t="n">
@@ -6186,13 +6198,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44137</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -6219,7 +6231,7 @@
       <c r="I18" t="n">
         <v>0.8600000000000001</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="K18" t="n">
@@ -6232,13 +6244,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44228</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44318</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -6265,7 +6277,7 @@
       <c r="I19" t="n">
         <v>1.073</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="K19" t="n">
@@ -6278,13 +6290,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44319</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44409</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -6311,7 +6323,7 @@
       <c r="I20" t="n">
         <v>1.348</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="K20" t="n">
@@ -6324,13 +6336,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44410</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44500</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -6357,7 +6369,7 @@
       <c r="I21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="K21" t="n">
@@ -6370,13 +6382,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>44501</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>44591</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -6403,7 +6415,7 @@
       <c r="I22" t="n">
         <v>1.754</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="K22" t="n">
@@ -6416,13 +6428,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>44682</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>44721</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -6449,7 +6461,7 @@
       <c r="I23" t="n">
         <v>2.017</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>44721</v>
       </c>
       <c r="K23" t="n">
@@ -6462,13 +6474,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>44683</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>44773</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -6495,7 +6507,7 @@
       <c r="I24" t="n">
         <v>2.312</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="K24" t="n">
@@ -6508,13 +6520,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>44774</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>44864</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -6541,7 +6553,7 @@
       <c r="I25" t="n">
         <v>2.653</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="K25" t="n">
@@ -6554,13 +6566,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>44865</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>44955</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -6587,7 +6599,7 @@
       <c r="I26" t="n">
         <v>2.974</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="K26" t="n">
@@ -6600,13 +6612,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>44956</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45046</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>45084</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -6633,7 +6645,7 @@
       <c r="I27" t="n">
         <v>3.196000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>45084</v>
       </c>
       <c r="K27" t="n">
@@ -6646,13 +6658,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45047</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45137</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -6679,7 +6691,7 @@
       <c r="I28" t="n">
         <v>3.255</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="K28" t="n">
@@ -6692,13 +6704,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45138</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45228</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>45274</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -6725,7 +6737,7 @@
       <c r="I29" t="n">
         <v>3.298</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>45274</v>
       </c>
       <c r="K29" t="n">
@@ -6738,13 +6750,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45229</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45326</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>45365</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -6771,7 +6783,7 @@
       <c r="I30" t="n">
         <v>2.701999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>45365</v>
       </c>
       <c r="K30" t="n">
@@ -6784,13 +6796,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45327</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45417</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>45456</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -6817,7 +6829,7 @@
       <c r="I31" t="n">
         <v>2.328999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>45456</v>
       </c>
       <c r="K31" t="n">
@@ -6830,13 +6842,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45418</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>45508</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -6863,7 +6875,7 @@
       <c r="I32" t="n">
         <v>1.154999999999999</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="K32" t="n">
@@ -6876,13 +6888,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>45509</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>45599</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -6909,7 +6921,7 @@
       <c r="I33" t="n">
         <v>1.23</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="K33" t="n">
@@ -6922,13 +6934,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>45600</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>45690</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -6955,7 +6967,7 @@
       <c r="I34" t="n">
         <v>2.086</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="K34" t="n">
@@ -6968,13 +6980,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>45691</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>45781</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -7001,7 +7013,7 @@
       <c r="I35" t="n">
         <v>2.674</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="K35" t="n">
@@ -7014,13 +7026,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>45782</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>45872</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -7047,7 +7059,7 @@
       <c r="I36" t="n">
         <v>3.924</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="K36" t="n">
@@ -7060,13 +7072,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>45873</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>45963</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -7093,7 +7105,7 @@
       <c r="I37" t="n">
         <v>4.77</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="K37" t="n">
@@ -7106,13 +7118,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>45964</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>46054</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -7139,7 +7151,7 @@
       <c r="I38" t="n">
         <v>5.13</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="K38" t="n">
@@ -7152,13 +7164,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>46055</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>46145</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -7185,7 +7197,7 @@
       <c r="I39" t="n">
         <v>6.01</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="K39" t="n">
@@ -7198,13 +7210,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>46146</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>46236</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -7231,7 +7243,7 @@
       <c r="I40" t="n">
         <v>7.84</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="K40" t="n">
@@ -7268,52 +7280,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>43252</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>43265</v>
       </c>
       <c r="C2" t="n">
@@ -7342,10 +7354,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>43343</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>43356</v>
       </c>
       <c r="C3" t="n">
@@ -7374,10 +7386,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>43434</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>43455</v>
       </c>
       <c r="C4" t="n">
@@ -7406,10 +7418,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>43525</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>43539</v>
       </c>
       <c r="C5" t="n">
@@ -7438,10 +7450,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>43616</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>43630</v>
       </c>
       <c r="C6" t="n">
@@ -7470,10 +7482,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>43707</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>43721</v>
       </c>
       <c r="C7" t="n">
@@ -7502,10 +7514,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>43798</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>43819</v>
       </c>
       <c r="C8" t="n">
@@ -7534,10 +7546,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>43889</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>43903</v>
       </c>
       <c r="C9" t="n">
@@ -7566,10 +7578,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>43980</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>43994</v>
       </c>
       <c r="C10" t="n">
@@ -7598,10 +7610,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>44071</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>44085</v>
       </c>
       <c r="C11" t="n">
@@ -7630,10 +7642,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>44162</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>44183</v>
       </c>
       <c r="C12" t="n">
@@ -7662,10 +7674,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>44253</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>44267</v>
       </c>
       <c r="C13" t="n">
@@ -7694,10 +7706,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>44344</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>44358</v>
       </c>
       <c r="C14" t="n">
@@ -7726,10 +7738,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>44435</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>44448</v>
       </c>
       <c r="C15" t="n">
@@ -7758,10 +7770,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>44526</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>44547</v>
       </c>
       <c r="C16" t="n">
@@ -7790,10 +7802,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>44617</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>44630</v>
       </c>
       <c r="C17" t="n">
@@ -7822,10 +7834,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>44708</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>44721</v>
       </c>
       <c r="C18" t="n">
@@ -7854,10 +7866,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>44799</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>44812</v>
       </c>
       <c r="C19" t="n">
@@ -7886,10 +7898,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>44890</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>44911</v>
       </c>
       <c r="C20" t="n">
@@ -7918,10 +7930,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>44981</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>44993</v>
       </c>
       <c r="C21" t="n">
@@ -7950,10 +7962,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>45072</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>45084</v>
       </c>
       <c r="C22" t="n">
@@ -7982,10 +7994,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>45163</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>45175</v>
       </c>
       <c r="C23" t="n">
@@ -8014,10 +8026,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>45254</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>45274</v>
       </c>
       <c r="C24" t="n">
@@ -8046,10 +8058,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>45352</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>45365</v>
       </c>
       <c r="C25" t="n">
@@ -8078,10 +8090,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>45443</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>45456</v>
       </c>
       <c r="C26" t="n">
@@ -8110,10 +8122,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>45534</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>45546</v>
       </c>
       <c r="C27" t="n">
@@ -8142,10 +8154,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>45625</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>45646</v>
       </c>
       <c r="C28" t="n">
@@ -8174,10 +8186,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>45716</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>45728</v>
       </c>
       <c r="C29" t="n">
@@ -8206,10 +8218,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>45807</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>45819</v>
       </c>
       <c r="C30" t="n">
@@ -8238,10 +8250,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>45898</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>45910</v>
       </c>
       <c r="C31" t="n">
@@ -8270,10 +8282,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>45989</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>46009</v>
       </c>
       <c r="C32" t="n">
@@ -8302,10 +8314,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>46080</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>46092</v>
       </c>
       <c r="C33" t="n">
@@ -8334,10 +8346,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>46171</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>46182</v>
       </c>
       <c r="C34" t="n">
@@ -8366,10 +8378,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>46262</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>46275</v>
       </c>
       <c r="C35" t="n">
@@ -8416,12 +8428,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/AVGO.xlsx
+++ b/salidas/empresas/AVGO.xlsx
@@ -498,7 +498,7 @@
         <v>40056</v>
       </c>
       <c r="B2" t="n">
-        <v>1.27504289150238</v>
+        <v>1.275042772293091</v>
       </c>
       <c r="C2" t="n">
         <v>1.820000052452087</v>
@@ -517,7 +517,7 @@
         <v>40086</v>
       </c>
       <c r="B3" t="n">
-        <v>1.195878386497498</v>
+        <v>1.195878148078918</v>
       </c>
       <c r="C3" t="n">
         <v>1.707000017166138</v>
@@ -536,7 +536,7 @@
         <v>40117</v>
       </c>
       <c r="B4" t="n">
-        <v>1.050859570503235</v>
+        <v>1.050859451293945</v>
       </c>
       <c r="C4" t="n">
         <v>1.5</v>
@@ -555,7 +555,7 @@
         <v>40147</v>
       </c>
       <c r="B5" t="n">
-        <v>1.111108541488647</v>
+        <v>1.111108899116516</v>
       </c>
       <c r="C5" t="n">
         <v>1.585999965667725</v>
@@ -574,7 +574,7 @@
         <v>40178</v>
       </c>
       <c r="B6" t="n">
-        <v>1.28134822845459</v>
+        <v>1.281347513198853</v>
       </c>
       <c r="C6" t="n">
         <v>1.828999996185303</v>
@@ -593,7 +593,7 @@
         <v>40209</v>
       </c>
       <c r="B7" t="n">
-        <v>1.217595458030701</v>
+        <v>1.217595934867859</v>
       </c>
       <c r="C7" t="n">
         <v>1.73800003528595</v>
@@ -612,7 +612,7 @@
         <v>40237</v>
       </c>
       <c r="B8" t="n">
-        <v>1.271539926528931</v>
+        <v>1.271540284156799</v>
       </c>
       <c r="C8" t="n">
         <v>1.815000057220459</v>
@@ -631,7 +631,7 @@
         <v>40268</v>
       </c>
       <c r="B9" t="n">
-        <v>1.440377712249756</v>
+        <v>1.440378189086914</v>
       </c>
       <c r="C9" t="n">
         <v>2.055999994277954</v>
@@ -650,7 +650,7 @@
         <v>40298</v>
       </c>
       <c r="B10" t="n">
-        <v>1.436875343322754</v>
+        <v>1.436875224113464</v>
       </c>
       <c r="C10" t="n">
         <v>2.051000118255615</v>
@@ -669,7 +669,7 @@
         <v>40329</v>
       </c>
       <c r="B11" t="n">
-        <v>1.446683645248413</v>
+        <v>1.446683764457703</v>
       </c>
       <c r="C11" t="n">
         <v>2.065000057220459</v>
@@ -707,7 +707,7 @@
         <v>40390</v>
       </c>
       <c r="B13" t="n">
-        <v>1.524446725845337</v>
+        <v>1.524447083473206</v>
       </c>
       <c r="C13" t="n">
         <v>2.176000118255615</v>
@@ -726,7 +726,7 @@
         <v>40421</v>
       </c>
       <c r="B14" t="n">
-        <v>1.411654472351074</v>
+        <v>1.411655068397522</v>
       </c>
       <c r="C14" t="n">
         <v>2.015000104904175</v>
@@ -745,7 +745,7 @@
         <v>40451</v>
       </c>
       <c r="B15" t="n">
-        <v>1.576989531517029</v>
+        <v>1.576990008354187</v>
       </c>
       <c r="C15" t="n">
         <v>2.250999927520752</v>
@@ -764,7 +764,7 @@
         <v>40482</v>
       </c>
       <c r="B16" t="n">
-        <v>1.72901451587677</v>
+        <v>1.729014277458191</v>
       </c>
       <c r="C16" t="n">
         <v>2.467999935150146</v>
@@ -783,7 +783,7 @@
         <v>40512</v>
       </c>
       <c r="B17" t="n">
-        <v>1.829195737838745</v>
+        <v>1.829196214675903</v>
       </c>
       <c r="C17" t="n">
         <v>2.611000061035156</v>
@@ -821,7 +821,7 @@
         <v>40574</v>
       </c>
       <c r="B19" t="n">
-        <v>2.016693115234375</v>
+        <v>2.016693353652954</v>
       </c>
       <c r="C19" t="n">
         <v>2.871000051498413</v>
@@ -840,7 +840,7 @@
         <v>40602</v>
       </c>
       <c r="B20" t="n">
-        <v>2.38757848739624</v>
+        <v>2.387577772140503</v>
       </c>
       <c r="C20" t="n">
         <v>3.398999929428101</v>
@@ -859,7 +859,7 @@
         <v>40633</v>
       </c>
       <c r="B21" t="n">
-        <v>2.190213680267334</v>
+        <v>2.190214395523071</v>
       </c>
       <c r="C21" t="n">
         <v>3.109999895095825</v>
@@ -897,7 +897,7 @@
         <v>40694</v>
       </c>
       <c r="B23" t="n">
-        <v>2.379656553268433</v>
+        <v>2.379656791687012</v>
       </c>
       <c r="C23" t="n">
         <v>3.378999948501587</v>
@@ -916,7 +916,7 @@
         <v>40724</v>
       </c>
       <c r="B24" t="n">
-        <v>2.683202981948853</v>
+        <v>2.683202266693115</v>
       </c>
       <c r="C24" t="n">
         <v>3.799999952316284</v>
@@ -935,7 +935,7 @@
         <v>40755</v>
       </c>
       <c r="B25" t="n">
-        <v>2.374634265899658</v>
+        <v>2.3746337890625</v>
       </c>
       <c r="C25" t="n">
         <v>3.36299991607666</v>
@@ -954,7 +954,7 @@
         <v>40786</v>
       </c>
       <c r="B26" t="n">
-        <v>2.337917327880859</v>
+        <v>2.337916851043701</v>
       </c>
       <c r="C26" t="n">
         <v>3.311000108718872</v>
@@ -973,7 +973,7 @@
         <v>40816</v>
       </c>
       <c r="B27" t="n">
-        <v>2.320893287658691</v>
+        <v>2.320892572402954</v>
       </c>
       <c r="C27" t="n">
         <v>3.276999950408936</v>
@@ -992,7 +992,7 @@
         <v>40847</v>
       </c>
       <c r="B28" t="n">
-        <v>2.391716241836548</v>
+        <v>2.39171576499939</v>
       </c>
       <c r="C28" t="n">
         <v>3.377000093460083</v>
@@ -1011,7 +1011,7 @@
         <v>40877</v>
       </c>
       <c r="B29" t="n">
-        <v>2.11904501914978</v>
+        <v>2.119044780731201</v>
       </c>
       <c r="C29" t="n">
         <v>2.992000102996826</v>
@@ -1030,7 +1030,7 @@
         <v>40908</v>
       </c>
       <c r="B30" t="n">
-        <v>2.052550315856934</v>
+        <v>2.05255126953125</v>
       </c>
       <c r="C30" t="n">
         <v>2.885999917984009</v>
@@ -1049,7 +1049,7 @@
         <v>40939</v>
       </c>
       <c r="B31" t="n">
-        <v>2.413844585418701</v>
+        <v>2.41384482383728</v>
       </c>
       <c r="C31" t="n">
         <v>3.394000053405762</v>
@@ -1068,7 +1068,7 @@
         <v>40968</v>
       </c>
       <c r="B32" t="n">
-        <v>2.674859046936035</v>
+        <v>2.674858570098877</v>
       </c>
       <c r="C32" t="n">
         <v>3.760999917984009</v>
@@ -1087,7 +1087,7 @@
         <v>40999</v>
       </c>
       <c r="B33" t="n">
-        <v>2.781326293945312</v>
+        <v>2.781326532363892</v>
       </c>
       <c r="C33" t="n">
         <v>3.897000074386597</v>
@@ -1106,7 +1106,7 @@
         <v>41029</v>
       </c>
       <c r="B34" t="n">
-        <v>2.460870504379272</v>
+        <v>2.460871696472168</v>
       </c>
       <c r="C34" t="n">
         <v>3.447999954223633</v>
@@ -1125,7 +1125,7 @@
         <v>41060</v>
       </c>
       <c r="B35" t="n">
-        <v>2.362379312515259</v>
+        <v>2.362380027770996</v>
       </c>
       <c r="C35" t="n">
         <v>3.309999942779541</v>
@@ -1144,7 +1144,7 @@
         <v>41090</v>
       </c>
       <c r="B36" t="n">
-        <v>2.573559045791626</v>
+        <v>2.57355809211731</v>
       </c>
       <c r="C36" t="n">
         <v>3.589999914169312</v>
@@ -1163,7 +1163,7 @@
         <v>41121</v>
       </c>
       <c r="B37" t="n">
-        <v>2.645244836807251</v>
+        <v>2.645245552062988</v>
       </c>
       <c r="C37" t="n">
         <v>3.690000057220459</v>
@@ -1201,7 +1201,7 @@
         <v>41182</v>
       </c>
       <c r="B39" t="n">
-        <v>2.511109113693237</v>
+        <v>2.511109590530396</v>
       </c>
       <c r="C39" t="n">
         <v>3.486999988555908</v>
@@ -1220,7 +1220,7 @@
         <v>41213</v>
       </c>
       <c r="B40" t="n">
-        <v>2.378604650497437</v>
+        <v>2.378604412078857</v>
       </c>
       <c r="C40" t="n">
         <v>3.302999973297119</v>
@@ -1239,7 +1239,7 @@
         <v>41243</v>
       </c>
       <c r="B41" t="n">
-        <v>2.52767276763916</v>
+        <v>2.527672290802002</v>
       </c>
       <c r="C41" t="n">
         <v>3.509999990463257</v>
@@ -1258,7 +1258,7 @@
         <v>41274</v>
       </c>
       <c r="B42" t="n">
-        <v>2.290488481521606</v>
+        <v>2.290489196777344</v>
       </c>
       <c r="C42" t="n">
         <v>3.164999961853027</v>
@@ -1277,7 +1277,7 @@
         <v>41305</v>
       </c>
       <c r="B43" t="n">
-        <v>2.588651895523071</v>
+        <v>2.588651180267334</v>
       </c>
       <c r="C43" t="n">
         <v>3.57699990272522</v>
@@ -1296,7 +1296,7 @@
         <v>41333</v>
       </c>
       <c r="B44" t="n">
-        <v>2.476477861404419</v>
+        <v>2.476479053497314</v>
       </c>
       <c r="C44" t="n">
         <v>3.421999931335449</v>
@@ -1315,7 +1315,7 @@
         <v>41364</v>
       </c>
       <c r="B45" t="n">
-        <v>2.613326787948608</v>
+        <v>2.613326072692871</v>
       </c>
       <c r="C45" t="n">
         <v>3.592000007629395</v>
@@ -1334,7 +1334,7 @@
         <v>41394</v>
       </c>
       <c r="B46" t="n">
-        <v>2.325220108032227</v>
+        <v>2.325220823287964</v>
       </c>
       <c r="C46" t="n">
         <v>3.196000099182129</v>
@@ -1391,7 +1391,7 @@
         <v>41486</v>
       </c>
       <c r="B49" t="n">
-        <v>2.684285163879395</v>
+        <v>2.684286117553711</v>
       </c>
       <c r="C49" t="n">
         <v>3.667999982833862</v>
@@ -1410,7 +1410,7 @@
         <v>41517</v>
       </c>
       <c r="B50" t="n">
-        <v>2.818207740783691</v>
+        <v>2.818207502365112</v>
       </c>
       <c r="C50" t="n">
         <v>3.851000070571899</v>
@@ -1429,7 +1429,7 @@
         <v>41547</v>
       </c>
       <c r="B51" t="n">
-        <v>3.171214580535889</v>
+        <v>3.171213388442993</v>
       </c>
       <c r="C51" t="n">
         <v>4.308000087738037</v>
@@ -1448,7 +1448,7 @@
         <v>41578</v>
       </c>
       <c r="B52" t="n">
-        <v>3.34420371055603</v>
+        <v>3.344202756881714</v>
       </c>
       <c r="C52" t="n">
         <v>4.543000221252441</v>
@@ -1467,7 +1467,7 @@
         <v>41608</v>
       </c>
       <c r="B53" t="n">
-        <v>3.292674541473389</v>
+        <v>3.29267430305481</v>
       </c>
       <c r="C53" t="n">
         <v>4.473000049591064</v>
@@ -1486,7 +1486,7 @@
         <v>41639</v>
       </c>
       <c r="B54" t="n">
-        <v>3.910867929458618</v>
+        <v>3.910868167877197</v>
       </c>
       <c r="C54" t="n">
         <v>5.288000106811523</v>
@@ -1505,7 +1505,7 @@
         <v>41670</v>
       </c>
       <c r="B55" t="n">
-        <v>4.041033744812012</v>
+        <v>4.041034698486328</v>
       </c>
       <c r="C55" t="n">
         <v>5.464000225067139</v>
@@ -1524,7 +1524,7 @@
         <v>41698</v>
       </c>
       <c r="B56" t="n">
-        <v>4.563172817230225</v>
+        <v>4.563174724578857</v>
       </c>
       <c r="C56" t="n">
         <v>6.170000076293945</v>
@@ -1543,7 +1543,7 @@
         <v>41729</v>
       </c>
       <c r="B57" t="n">
-        <v>4.783967018127441</v>
+        <v>4.783968448638916</v>
       </c>
       <c r="C57" t="n">
         <v>6.440999984741211</v>
@@ -1562,7 +1562,7 @@
         <v>41759</v>
       </c>
       <c r="B58" t="n">
-        <v>4.716378211975098</v>
+        <v>4.716379642486572</v>
       </c>
       <c r="C58" t="n">
         <v>6.349999904632568</v>
@@ -1581,7 +1581,7 @@
         <v>41790</v>
       </c>
       <c r="B59" t="n">
-        <v>5.248920440673828</v>
+        <v>5.248920917510986</v>
       </c>
       <c r="C59" t="n">
         <v>7.066999912261963</v>
@@ -1600,7 +1600,7 @@
         <v>41820</v>
       </c>
       <c r="B60" t="n">
-        <v>5.374894618988037</v>
+        <v>5.374892711639404</v>
       </c>
       <c r="C60" t="n">
         <v>7.206999778747559</v>
@@ -1619,7 +1619,7 @@
         <v>41851</v>
       </c>
       <c r="B61" t="n">
-        <v>5.174278259277344</v>
+        <v>5.174277782440186</v>
       </c>
       <c r="C61" t="n">
         <v>6.938000202178955</v>
@@ -1657,7 +1657,7 @@
         <v>41912</v>
       </c>
       <c r="B63" t="n">
-        <v>6.512057781219482</v>
+        <v>6.512058734893799</v>
       </c>
       <c r="C63" t="n">
         <v>8.699999809265137</v>
@@ -1676,7 +1676,7 @@
         <v>41943</v>
       </c>
       <c r="B64" t="n">
-        <v>6.455920696258545</v>
+        <v>6.455919742584229</v>
       </c>
       <c r="C64" t="n">
         <v>8.625</v>
@@ -1714,7 +1714,7 @@
         <v>42004</v>
       </c>
       <c r="B66" t="n">
-        <v>7.556460380554199</v>
+        <v>7.556458950042725</v>
       </c>
       <c r="C66" t="n">
         <v>10.05900001525879</v>
@@ -1733,7 +1733,7 @@
         <v>42035</v>
       </c>
       <c r="B67" t="n">
-        <v>7.728488922119141</v>
+        <v>7.728488445281982</v>
       </c>
       <c r="C67" t="n">
         <v>10.28800010681152</v>
@@ -1790,7 +1790,7 @@
         <v>42124</v>
       </c>
       <c r="B70" t="n">
-        <v>8.806107521057129</v>
+        <v>8.806108474731445</v>
       </c>
       <c r="C70" t="n">
         <v>11.6879997253418</v>
@@ -1809,7 +1809,7 @@
         <v>42155</v>
       </c>
       <c r="B71" t="n">
-        <v>11.1560640335083</v>
+        <v>11.15605926513672</v>
       </c>
       <c r="C71" t="n">
         <v>14.80700016021729</v>
@@ -1828,7 +1828,7 @@
         <v>42185</v>
       </c>
       <c r="B72" t="n">
-        <v>10.04366207122803</v>
+        <v>10.04365634918213</v>
       </c>
       <c r="C72" t="n">
         <v>13.29300022125244</v>
@@ -1847,7 +1847,7 @@
         <v>42216</v>
       </c>
       <c r="B73" t="n">
-        <v>9.455080986022949</v>
+        <v>9.455079078674316</v>
       </c>
       <c r="C73" t="n">
         <v>12.51399993896484</v>
@@ -1866,7 +1866,7 @@
         <v>42247</v>
       </c>
       <c r="B74" t="n">
-        <v>9.517789840698242</v>
+        <v>9.517791748046875</v>
       </c>
       <c r="C74" t="n">
         <v>12.59700012207031</v>
@@ -1885,7 +1885,7 @@
         <v>42277</v>
       </c>
       <c r="B75" t="n">
-        <v>9.474870681762695</v>
+        <v>9.474868774414062</v>
       </c>
       <c r="C75" t="n">
         <v>12.50100040435791</v>
@@ -1904,7 +1904,7 @@
         <v>42308</v>
       </c>
       <c r="B76" t="n">
-        <v>9.332379341125488</v>
+        <v>9.332377433776855</v>
       </c>
       <c r="C76" t="n">
         <v>12.3129997253418</v>
@@ -1942,7 +1942,7 @@
         <v>42369</v>
       </c>
       <c r="B78" t="n">
-        <v>11.03522777557373</v>
+        <v>11.035231590271</v>
       </c>
       <c r="C78" t="n">
         <v>14.51500034332275</v>
@@ -1980,7 +1980,7 @@
         <v>42429</v>
       </c>
       <c r="B80" t="n">
-        <v>10.18525409698486</v>
+        <v>10.1852560043335</v>
       </c>
       <c r="C80" t="n">
         <v>13.39700031280518</v>
@@ -1999,7 +1999,7 @@
         <v>42460</v>
       </c>
       <c r="B81" t="n">
-        <v>11.7849702835083</v>
+        <v>11.78496932983398</v>
       </c>
       <c r="C81" t="n">
         <v>15.44999980926514</v>
@@ -2018,7 +2018,7 @@
         <v>42490</v>
       </c>
       <c r="B82" t="n">
-        <v>11.11753749847412</v>
+        <v>11.11753463745117</v>
       </c>
       <c r="C82" t="n">
         <v>14.57499980926514</v>
@@ -2037,7 +2037,7 @@
         <v>42521</v>
       </c>
       <c r="B83" t="n">
-        <v>11.77429294586182</v>
+        <v>11.77429103851318</v>
       </c>
       <c r="C83" t="n">
         <v>15.43599987030029</v>
@@ -2056,7 +2056,7 @@
         <v>42551</v>
       </c>
       <c r="B84" t="n">
-        <v>11.89101505279541</v>
+        <v>11.89101600646973</v>
       </c>
       <c r="C84" t="n">
         <v>15.53999996185303</v>
@@ -2075,7 +2075,7 @@
         <v>42582</v>
       </c>
       <c r="B85" t="n">
-        <v>12.39450836181641</v>
+        <v>12.39450931549072</v>
       </c>
       <c r="C85" t="n">
         <v>16.19799995422363</v>
@@ -2094,7 +2094,7 @@
         <v>42613</v>
       </c>
       <c r="B86" t="n">
-        <v>13.49944019317627</v>
+        <v>13.49943828582764</v>
       </c>
       <c r="C86" t="n">
         <v>17.64200019836426</v>
@@ -2113,7 +2113,7 @@
         <v>42643</v>
       </c>
       <c r="B87" t="n">
-        <v>13.24083137512207</v>
+        <v>13.2408332824707</v>
       </c>
       <c r="C87" t="n">
         <v>17.25200080871582</v>
@@ -2151,7 +2151,7 @@
         <v>42704</v>
       </c>
       <c r="B89" t="n">
-        <v>13.08502578735352</v>
+        <v>13.08502960205078</v>
       </c>
       <c r="C89" t="n">
         <v>17.04899978637695</v>
@@ -2170,7 +2170,7 @@
         <v>42735</v>
       </c>
       <c r="B90" t="n">
-        <v>13.64457893371582</v>
+        <v>13.64457511901855</v>
       </c>
       <c r="C90" t="n">
         <v>17.67700004577637</v>
@@ -2189,7 +2189,7 @@
         <v>42766</v>
       </c>
       <c r="B91" t="n">
-        <v>15.39907073974609</v>
+        <v>15.39906692504883</v>
       </c>
       <c r="C91" t="n">
         <v>19.95000076293945</v>
@@ -2227,7 +2227,7 @@
         <v>42825</v>
       </c>
       <c r="B93" t="n">
-        <v>16.97779655456543</v>
+        <v>16.9778003692627</v>
       </c>
       <c r="C93" t="n">
         <v>21.89599990844727</v>
@@ -2246,7 +2246,7 @@
         <v>42855</v>
       </c>
       <c r="B94" t="n">
-        <v>17.12124443054199</v>
+        <v>17.12124824523926</v>
       </c>
       <c r="C94" t="n">
         <v>22.08099937438965</v>
@@ -2265,7 +2265,7 @@
         <v>42886</v>
       </c>
       <c r="B95" t="n">
-        <v>18.56888771057129</v>
+        <v>18.56889152526855</v>
       </c>
       <c r="C95" t="n">
         <v>23.94799995422363</v>
@@ -2284,7 +2284,7 @@
         <v>42916</v>
       </c>
       <c r="B96" t="n">
-        <v>18.14726638793945</v>
+        <v>18.14727783203125</v>
       </c>
       <c r="C96" t="n">
         <v>23.30500030517578</v>
@@ -2303,7 +2303,7 @@
         <v>42947</v>
       </c>
       <c r="B97" t="n">
-        <v>19.20705795288086</v>
+        <v>19.20706558227539</v>
       </c>
       <c r="C97" t="n">
         <v>24.66600036621094</v>
@@ -2322,7 +2322,7 @@
         <v>42978</v>
       </c>
       <c r="B98" t="n">
-        <v>19.62833213806152</v>
+        <v>19.62833023071289</v>
       </c>
       <c r="C98" t="n">
         <v>25.20700073242188</v>
@@ -2341,7 +2341,7 @@
         <v>43008</v>
       </c>
       <c r="B99" t="n">
-        <v>18.96344375610352</v>
+        <v>18.96343994140625</v>
       </c>
       <c r="C99" t="n">
         <v>24.25399971008301</v>
@@ -2379,7 +2379,7 @@
         <v>43069</v>
       </c>
       <c r="B101" t="n">
-        <v>21.73126220703125</v>
+        <v>21.73125839233398</v>
       </c>
       <c r="C101" t="n">
         <v>27.79400062561035</v>
@@ -2398,7 +2398,7 @@
         <v>43100</v>
       </c>
       <c r="B102" t="n">
-        <v>20.2193660736084</v>
+        <v>20.2193717956543</v>
       </c>
       <c r="C102" t="n">
         <v>25.69000053405762</v>
@@ -2417,7 +2417,7 @@
         <v>43131</v>
       </c>
       <c r="B103" t="n">
-        <v>19.52124977111816</v>
+        <v>19.52124786376953</v>
       </c>
       <c r="C103" t="n">
         <v>24.80299949645996</v>
@@ -2436,7 +2436,7 @@
         <v>43159</v>
       </c>
       <c r="B104" t="n">
-        <v>19.39767646789551</v>
+        <v>19.39768218994141</v>
       </c>
       <c r="C104" t="n">
         <v>24.64599990844727</v>
@@ -2455,7 +2455,7 @@
         <v>43190</v>
       </c>
       <c r="B105" t="n">
-        <v>18.81864166259766</v>
+        <v>18.81864738464355</v>
       </c>
       <c r="C105" t="n">
         <v>23.56500053405762</v>
@@ -2493,7 +2493,7 @@
         <v>43251</v>
       </c>
       <c r="B107" t="n">
-        <v>20.12992858886719</v>
+        <v>20.12991905212402</v>
       </c>
       <c r="C107" t="n">
         <v>25.20700073242188</v>
@@ -2537,7 +2537,7 @@
         <v>43312</v>
       </c>
       <c r="B109" t="n">
-        <v>17.94770050048828</v>
+        <v>17.94770240783691</v>
       </c>
       <c r="C109" t="n">
         <v>22.17700004577637</v>
@@ -2562,7 +2562,7 @@
         <v>43343</v>
       </c>
       <c r="B110" t="n">
-        <v>17.7259578704834</v>
+        <v>17.72595596313477</v>
       </c>
       <c r="C110" t="n">
         <v>21.90299987792969</v>
@@ -2587,7 +2587,7 @@
         <v>43373</v>
       </c>
       <c r="B111" t="n">
-        <v>20.11762237548828</v>
+        <v>20.11762046813965</v>
       </c>
       <c r="C111" t="n">
         <v>24.67300033569336</v>
@@ -2637,7 +2637,7 @@
         <v>43434</v>
       </c>
       <c r="B113" t="n">
-        <v>19.35769653320312</v>
+        <v>19.35769271850586</v>
       </c>
       <c r="C113" t="n">
         <v>23.74099922180176</v>
@@ -2662,7 +2662,7 @@
         <v>43465</v>
       </c>
       <c r="B114" t="n">
-        <v>20.95170402526855</v>
+        <v>20.95170211791992</v>
       </c>
       <c r="C114" t="n">
         <v>25.42799949645996</v>
@@ -2691,7 +2691,7 @@
         <v>43496</v>
       </c>
       <c r="B115" t="n">
-        <v>22.10277366638184</v>
+        <v>22.10277938842773</v>
       </c>
       <c r="C115" t="n">
         <v>26.82500076293945</v>
@@ -2749,7 +2749,7 @@
         <v>43555</v>
       </c>
       <c r="B117" t="n">
-        <v>24.99869155883789</v>
+        <v>24.99868965148926</v>
       </c>
       <c r="C117" t="n">
         <v>30.07099914550781</v>
@@ -2778,7 +2778,7 @@
         <v>43585</v>
       </c>
       <c r="B118" t="n">
-        <v>26.46929550170898</v>
+        <v>26.46929168701172</v>
       </c>
       <c r="C118" t="n">
         <v>31.84000015258789</v>
@@ -2836,7 +2836,7 @@
         <v>43646</v>
       </c>
       <c r="B120" t="n">
-        <v>24.15987586975098</v>
+        <v>24.15987205505371</v>
       </c>
       <c r="C120" t="n">
         <v>28.7859992980957</v>
@@ -2894,7 +2894,7 @@
         <v>43708</v>
       </c>
       <c r="B122" t="n">
-        <v>23.72176742553711</v>
+        <v>23.72176361083984</v>
       </c>
       <c r="C122" t="n">
         <v>28.26399993896484</v>
@@ -2923,7 +2923,7 @@
         <v>43738</v>
       </c>
       <c r="B123" t="n">
-        <v>23.38355445861816</v>
+        <v>23.38355255126953</v>
       </c>
       <c r="C123" t="n">
         <v>27.60700035095215</v>
@@ -2952,7 +2952,7 @@
         <v>43769</v>
       </c>
       <c r="B124" t="n">
-        <v>24.80484580993652</v>
+        <v>24.80484390258789</v>
       </c>
       <c r="C124" t="n">
         <v>29.28499984741211</v>
@@ -3010,7 +3010,7 @@
         <v>43830</v>
       </c>
       <c r="B126" t="n">
-        <v>27.03851699829102</v>
+        <v>27.03851509094238</v>
       </c>
       <c r="C126" t="n">
         <v>31.60199928283691</v>
@@ -3039,7 +3039,7 @@
         <v>43861</v>
       </c>
       <c r="B127" t="n">
-        <v>26.10934066772461</v>
+        <v>26.10934448242188</v>
       </c>
       <c r="C127" t="n">
         <v>30.51600074768066</v>
@@ -3068,7 +3068,7 @@
         <v>43890</v>
       </c>
       <c r="B128" t="n">
-        <v>23.32522964477539</v>
+        <v>23.32523345947266</v>
       </c>
       <c r="C128" t="n">
         <v>27.26199913024902</v>
@@ -3097,7 +3097,7 @@
         <v>43921</v>
       </c>
       <c r="B129" t="n">
-        <v>20.6309757232666</v>
+        <v>20.63097953796387</v>
       </c>
       <c r="C129" t="n">
         <v>23.70999908447266</v>
@@ -3126,7 +3126,7 @@
         <v>43951</v>
       </c>
       <c r="B130" t="n">
-        <v>23.63469696044922</v>
+        <v>23.63470077514648</v>
       </c>
       <c r="C130" t="n">
         <v>27.16200065612793</v>
@@ -3155,7 +3155,7 @@
         <v>43982</v>
       </c>
       <c r="B131" t="n">
-        <v>25.34452247619629</v>
+        <v>25.34452819824219</v>
       </c>
       <c r="C131" t="n">
         <v>29.12700080871582</v>
@@ -3184,7 +3184,7 @@
         <v>44012</v>
       </c>
       <c r="B132" t="n">
-        <v>27.74536895751953</v>
+        <v>27.74536514282227</v>
       </c>
       <c r="C132" t="n">
         <v>31.56100082397461</v>
@@ -3242,7 +3242,7 @@
         <v>44074</v>
       </c>
       <c r="B134" t="n">
-        <v>30.51805877685547</v>
+        <v>30.51806259155273</v>
       </c>
       <c r="C134" t="n">
         <v>34.71500015258789</v>
@@ -3271,7 +3271,7 @@
         <v>44104</v>
       </c>
       <c r="B135" t="n">
-        <v>32.31946182250977</v>
+        <v>32.3194694519043</v>
       </c>
       <c r="C135" t="n">
         <v>36.43199920654297</v>
@@ -3300,7 +3300,7 @@
         <v>44135</v>
       </c>
       <c r="B136" t="n">
-        <v>31.01629638671875</v>
+        <v>31.01629829406738</v>
       </c>
       <c r="C136" t="n">
         <v>34.9630012512207</v>
@@ -3329,7 +3329,7 @@
         <v>44165</v>
       </c>
       <c r="B137" t="n">
-        <v>35.62487030029297</v>
+        <v>35.62488174438477</v>
       </c>
       <c r="C137" t="n">
         <v>40.15800094604492</v>
@@ -3387,7 +3387,7 @@
         <v>44227</v>
       </c>
       <c r="B139" t="n">
-        <v>40.30517578125</v>
+        <v>40.3051872253418</v>
       </c>
       <c r="C139" t="n">
         <v>45.04999923706055</v>
@@ -3416,7 +3416,7 @@
         <v>44255</v>
       </c>
       <c r="B140" t="n">
-        <v>42.03816604614258</v>
+        <v>42.03817367553711</v>
       </c>
       <c r="C140" t="n">
         <v>46.98699951171875</v>
@@ -3474,7 +3474,7 @@
         <v>44316</v>
       </c>
       <c r="B142" t="n">
-        <v>41.13418579101562</v>
+        <v>41.13417053222656</v>
       </c>
       <c r="C142" t="n">
         <v>45.61999893188477</v>
@@ -3532,7 +3532,7 @@
         <v>44377</v>
       </c>
       <c r="B144" t="n">
-        <v>43.33178329467773</v>
+        <v>43.331787109375</v>
       </c>
       <c r="C144" t="n">
         <v>47.68399810791016</v>
@@ -3561,7 +3561,7 @@
         <v>44408</v>
       </c>
       <c r="B145" t="n">
-        <v>44.10965347290039</v>
+        <v>44.10966491699219</v>
       </c>
       <c r="C145" t="n">
         <v>48.54000091552734</v>
@@ -3677,7 +3677,7 @@
         <v>44530</v>
       </c>
       <c r="B149" t="n">
-        <v>50.68319702148438</v>
+        <v>50.68319320678711</v>
       </c>
       <c r="C149" t="n">
         <v>55.36800003051758</v>
@@ -3706,7 +3706,7 @@
         <v>44561</v>
       </c>
       <c r="B150" t="n">
-        <v>61.30046463012695</v>
+        <v>61.30045318603516</v>
       </c>
       <c r="C150" t="n">
         <v>66.54100036621094</v>
@@ -3735,7 +3735,7 @@
         <v>44592</v>
       </c>
       <c r="B151" t="n">
-        <v>53.97380828857422</v>
+        <v>53.97382354736328</v>
       </c>
       <c r="C151" t="n">
         <v>58.5880012512207</v>
@@ -3764,7 +3764,7 @@
         <v>44620</v>
       </c>
       <c r="B152" t="n">
-        <v>54.11753845214844</v>
+        <v>54.11752319335938</v>
       </c>
       <c r="C152" t="n">
         <v>58.74399948120117</v>
@@ -3822,7 +3822,7 @@
         <v>44681</v>
       </c>
       <c r="B154" t="n">
-        <v>51.41819381713867</v>
+        <v>51.41818618774414</v>
       </c>
       <c r="C154" t="n">
         <v>55.43899917602539</v>
@@ -3851,7 +3851,7 @@
         <v>44712</v>
       </c>
       <c r="B155" t="n">
-        <v>53.80549621582031</v>
+        <v>53.80550765991211</v>
       </c>
       <c r="C155" t="n">
         <v>58.01300048828125</v>
@@ -3880,7 +3880,7 @@
         <v>44742</v>
       </c>
       <c r="B156" t="n">
-        <v>45.43111801147461</v>
+        <v>45.43112182617188</v>
       </c>
       <c r="C156" t="n">
         <v>48.58100128173828</v>
@@ -3938,7 +3938,7 @@
         <v>44804</v>
       </c>
       <c r="B158" t="n">
-        <v>46.67488479614258</v>
+        <v>46.67488861083984</v>
       </c>
       <c r="C158" t="n">
         <v>49.9109992980957</v>
@@ -3967,7 +3967,7 @@
         <v>44834</v>
       </c>
       <c r="B159" t="n">
-        <v>41.87031173706055</v>
+        <v>41.87030792236328</v>
       </c>
       <c r="C159" t="n">
         <v>44.4010009765625</v>
@@ -3996,7 +3996,7 @@
         <v>44865</v>
       </c>
       <c r="B160" t="n">
-        <v>44.33249282836914</v>
+        <v>44.33250045776367</v>
       </c>
       <c r="C160" t="n">
         <v>47.01200103759766</v>
@@ -4025,7 +4025,7 @@
         <v>44895</v>
       </c>
       <c r="B161" t="n">
-        <v>51.96234130859375</v>
+        <v>51.96235275268555</v>
       </c>
       <c r="C161" t="n">
         <v>55.10300064086914</v>
@@ -4054,7 +4054,7 @@
         <v>44926</v>
       </c>
       <c r="B162" t="n">
-        <v>53.16609954833984</v>
+        <v>53.16610717773438</v>
       </c>
       <c r="C162" t="n">
         <v>55.91299819946289</v>
@@ -4141,7 +4141,7 @@
         <v>45016</v>
       </c>
       <c r="B165" t="n">
-        <v>61.44131088256836</v>
+        <v>61.44130706787109</v>
       </c>
       <c r="C165" t="n">
         <v>64.15399932861328</v>
@@ -4170,7 +4170,7 @@
         <v>45046</v>
       </c>
       <c r="B166" t="n">
-        <v>60.00090408325195</v>
+        <v>60.00090789794922</v>
       </c>
       <c r="C166" t="n">
         <v>62.65000152587891</v>
@@ -4199,7 +4199,7 @@
         <v>45077</v>
       </c>
       <c r="B167" t="n">
-        <v>77.37961578369141</v>
+        <v>77.37960815429688</v>
       </c>
       <c r="C167" t="n">
         <v>80.79599761962891</v>
@@ -4228,7 +4228,7 @@
         <v>45107</v>
       </c>
       <c r="B168" t="n">
-        <v>83.51773834228516</v>
+        <v>83.51772308349609</v>
       </c>
       <c r="C168" t="n">
         <v>86.74299621582031</v>
@@ -4257,7 +4257,7 @@
         <v>45138</v>
       </c>
       <c r="B169" t="n">
-        <v>86.52365112304688</v>
+        <v>86.52365875244141</v>
       </c>
       <c r="C169" t="n">
         <v>89.86499786376953</v>
@@ -4286,7 +4286,7 @@
         <v>45169</v>
       </c>
       <c r="B170" t="n">
-        <v>88.85752868652344</v>
+        <v>88.85752105712891</v>
       </c>
       <c r="C170" t="n">
         <v>92.28900146484375</v>
@@ -4315,7 +4315,7 @@
         <v>45199</v>
       </c>
       <c r="B171" t="n">
-        <v>80.40530395507812</v>
+        <v>80.40529632568359</v>
       </c>
       <c r="C171" t="n">
         <v>83.05799865722656</v>
@@ -4373,7 +4373,7 @@
         <v>45260</v>
       </c>
       <c r="B173" t="n">
-        <v>89.61641693115234</v>
+        <v>89.61640930175781</v>
       </c>
       <c r="C173" t="n">
         <v>92.572998046875</v>
@@ -4402,7 +4402,7 @@
         <v>45291</v>
       </c>
       <c r="B174" t="n">
-        <v>108.5568161010742</v>
+        <v>108.5568084716797</v>
       </c>
       <c r="C174" t="n">
         <v>111.625</v>
@@ -4431,7 +4431,7 @@
         <v>45322</v>
       </c>
       <c r="B175" t="n">
-        <v>114.756591796875</v>
+        <v>114.7565841674805</v>
       </c>
       <c r="C175" t="n">
         <v>118</v>
@@ -4489,7 +4489,7 @@
         <v>45382</v>
       </c>
       <c r="B177" t="n">
-        <v>129.4468383789062</v>
+        <v>129.4468536376953</v>
       </c>
       <c r="C177" t="n">
         <v>132.5410003662109</v>
@@ -4518,7 +4518,7 @@
         <v>45412</v>
       </c>
       <c r="B178" t="n">
-        <v>126.9915390014648</v>
+        <v>126.9915237426758</v>
       </c>
       <c r="C178" t="n">
         <v>130.0269927978516</v>
@@ -4576,7 +4576,7 @@
         <v>45473</v>
       </c>
       <c r="B180" t="n">
-        <v>157.3027954101562</v>
+        <v>157.3028106689453</v>
       </c>
       <c r="C180" t="n">
         <v>160.5529937744141</v>
@@ -4634,7 +4634,7 @@
         <v>45535</v>
       </c>
       <c r="B182" t="n">
-        <v>159.52392578125</v>
+        <v>159.5239410400391</v>
       </c>
       <c r="C182" t="n">
         <v>162.8200073242188</v>
@@ -4663,7 +4663,7 @@
         <v>45565</v>
       </c>
       <c r="B183" t="n">
-        <v>169.5638427734375</v>
+        <v>169.5638275146484</v>
       </c>
       <c r="C183" t="n">
         <v>172.5</v>
@@ -4750,7 +4750,7 @@
         <v>45657</v>
       </c>
       <c r="B186" t="n">
-        <v>228.50439453125</v>
+        <v>228.5044097900391</v>
       </c>
       <c r="C186" t="n">
         <v>231.8399963378906</v>
@@ -4779,7 +4779,7 @@
         <v>45688</v>
       </c>
       <c r="B187" t="n">
-        <v>218.0865020751953</v>
+        <v>218.0864715576172</v>
       </c>
       <c r="C187" t="n">
         <v>221.2700042724609</v>
@@ -4837,7 +4837,7 @@
         <v>45747</v>
       </c>
       <c r="B189" t="n">
-        <v>165.5204467773438</v>
+        <v>165.5204315185547</v>
       </c>
       <c r="C189" t="n">
         <v>167.4299926757812</v>
@@ -4895,7 +4895,7 @@
         <v>45808</v>
       </c>
       <c r="B191" t="n">
-        <v>239.3091735839844</v>
+        <v>239.3091888427734</v>
       </c>
       <c r="C191" t="n">
         <v>242.0700073242188</v>
@@ -4924,7 +4924,7 @@
         <v>45838</v>
       </c>
       <c r="B192" t="n">
-        <v>273.1475830078125</v>
+        <v>273.1475524902344</v>
       </c>
       <c r="C192" t="n">
         <v>275.6499938964844</v>
@@ -4953,7 +4953,7 @@
         <v>45869</v>
       </c>
       <c r="B193" t="n">
-        <v>291.0337829589844</v>
+        <v>291.0337219238281</v>
       </c>
       <c r="C193" t="n">
         <v>293.7000122070312</v>
@@ -4982,7 +4982,7 @@
         <v>45900</v>
       </c>
       <c r="B194" t="n">
-        <v>294.6902465820312</v>
+        <v>294.6902160644531</v>
       </c>
       <c r="C194" t="n">
         <v>297.3900146484375</v>
@@ -5011,7 +5011,7 @@
         <v>45930</v>
       </c>
       <c r="B195" t="n">
-        <v>327.4751586914062</v>
+        <v>327.47509765625</v>
       </c>
       <c r="C195" t="n">
         <v>329.9100036621094</v>
@@ -5040,7 +5040,7 @@
         <v>45961</v>
       </c>
       <c r="B196" t="n">
-        <v>366.9020080566406</v>
+        <v>366.9019775390625</v>
       </c>
       <c r="C196" t="n">
         <v>369.6300048828125</v>
@@ -5069,7 +5069,7 @@
         <v>45991</v>
       </c>
       <c r="B197" t="n">
-        <v>399.9859619140625</v>
+        <v>399.9859924316406</v>
       </c>
       <c r="C197" t="n">
         <v>402.9599914550781</v>
@@ -5185,7 +5185,7 @@
         <v>46112</v>
       </c>
       <c r="B201" t="n">
-        <v>308.459228515625</v>
+        <v>308.4592590332031</v>
       </c>
       <c r="C201" t="n">
         <v>309.510009765625</v>
